--- a/results/tables/metric_comparisons.xlsx
+++ b/results/tables/metric_comparisons.xlsx
@@ -524,7 +524,7 @@
         <v>0.9220779220776228</v>
       </c>
       <c r="G3">
-        <v>0.1028068367053162</v>
+        <v>0.1028068367053161</v>
       </c>
       <c r="H3">
         <v>0.1007442536453406</v>
@@ -550,10 +550,10 @@
         <v>0.9888888888886144</v>
       </c>
       <c r="G4">
-        <v>0.00323525130410086</v>
+        <v>0.0032352513041008</v>
       </c>
       <c r="H4">
-        <v>0.002466177917085588</v>
+        <v>0.0024661779170855</v>
       </c>
     </row>
   </sheetData>
@@ -649,10 +649,10 @@
         <v>0.9220779220776228</v>
       </c>
       <c r="F4">
-        <v>0.00323525130410086</v>
+        <v>0.0032352513041008</v>
       </c>
       <c r="G4">
-        <v>0.002466177917085588</v>
+        <v>0.0024661779170855</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -695,7 +695,7 @@
         <v>0.9888888888886144</v>
       </c>
       <c r="F6">
-        <v>0.1028068367053162</v>
+        <v>0.1028068367053161</v>
       </c>
       <c r="G6">
         <v>0.1007442536453406</v>
@@ -812,16 +812,16 @@
         <v>0.9915730337075866</v>
       </c>
       <c r="E4">
-        <v>0.6091298145506421</v>
+        <v>0.609129814550642</v>
       </c>
       <c r="F4">
         <v>0.5657051282050375</v>
       </c>
       <c r="G4">
-        <v>0.2833014943382957</v>
+        <v>0.2833014943382956</v>
       </c>
       <c r="H4">
-        <v>0.2282243296504021</v>
+        <v>0.228224329650402</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -841,7 +841,7 @@
         <v>0.9999999999997192</v>
       </c>
       <c r="E5">
-        <v>0.8844507845934381</v>
+        <v>0.884450784593438</v>
       </c>
       <c r="F5">
         <v>0.8146453089242988</v>
@@ -870,16 +870,16 @@
         <v>0.760563380281476</v>
       </c>
       <c r="E6">
-        <v>0.7974322396576321</v>
+        <v>0.797432239657632</v>
       </c>
       <c r="F6">
         <v>0.825688073394243</v>
       </c>
       <c r="G6">
-        <v>0.1487569768320431</v>
+        <v>0.148756976832043</v>
       </c>
       <c r="H6">
-        <v>0.1456626318395138</v>
+        <v>0.1456626318395137</v>
       </c>
       <c r="I6">
         <v>19</v>
@@ -905,10 +905,10 @@
         <v>0.7231404958676192</v>
       </c>
       <c r="G7">
-        <v>0.05125840905715118</v>
+        <v>0.0512584090571511</v>
       </c>
       <c r="H7">
-        <v>0.04970996764798959</v>
+        <v>0.0497099676479895</v>
       </c>
       <c r="I7">
         <v>19</v>
@@ -934,7 +934,7 @@
         <v>0.9834710743798944</v>
       </c>
       <c r="G8">
-        <v>20.68767307563261</v>
+        <v>20.68767307563262</v>
       </c>
       <c r="H8">
         <v>23.57665980945934</v>
@@ -992,10 +992,10 @@
         <v>0.9216216216213724</v>
       </c>
       <c r="G10">
-        <v>0.01350367081944238</v>
+        <v>0.0135036708194423</v>
       </c>
       <c r="H10">
-        <v>0.01074900710955262</v>
+        <v>0.0107490071095526</v>
       </c>
       <c r="I10">
         <v>39</v>
@@ -1050,7 +1050,7 @@
         <v>0.9220779220776228</v>
       </c>
       <c r="G12">
-        <v>0.1028068367053162</v>
+        <v>0.1028068367053161</v>
       </c>
       <c r="H12">
         <v>0.1007442536453406</v>
@@ -1079,10 +1079,10 @@
         <v>0.9435028248584906</v>
       </c>
       <c r="G13">
-        <v>0.004665813461708074</v>
+        <v>0.004665813461708</v>
       </c>
       <c r="H13">
-        <v>0.004680642470096547</v>
+        <v>0.0046806424700965</v>
       </c>
       <c r="I13">
         <v>59</v>
@@ -1137,7 +1137,7 @@
         <v>0.9220779220776228</v>
       </c>
       <c r="G15">
-        <v>0.1028068367053162</v>
+        <v>0.1028068367053161</v>
       </c>
       <c r="H15">
         <v>0.1007442536453406</v>
@@ -1166,10 +1166,10 @@
         <v>0.9888888888886144</v>
       </c>
       <c r="G16">
-        <v>0.00323525130410086</v>
+        <v>0.0032352513041008</v>
       </c>
       <c r="H16">
-        <v>0.002466177917085588</v>
+        <v>0.0024661779170855</v>
       </c>
       <c r="I16">
         <v>79</v>
@@ -1277,16 +1277,16 @@
         <v>0.008498583569405211</v>
       </c>
       <c r="E4">
-        <v>0.6323185011709598</v>
+        <v>0.6323185011709601</v>
       </c>
       <c r="F4">
         <v>0.7480642115200973</v>
       </c>
       <c r="G4">
-        <v>-0.9885801827072696</v>
+        <v>-0.9885801827072698</v>
       </c>
       <c r="H4">
-        <v>-0.9891940621717968</v>
+        <v>-0.9891940621717972</v>
       </c>
     </row>
   </sheetData>
